--- a/config/excel/equipments.xlsx
+++ b/config/excel/equipments.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20371"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336C9B7E-E2B5-4D30-ACDE-B7AFC1D3D127}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F30698E-3043-4497-87E1-0A22058B1F91}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="74">
   <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -279,6 +279,41 @@
   </si>
   <si>
     <t>此sheet是构思草稿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>equip_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>equip_02</t>
+  </si>
+  <si>
+    <t>equip_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>equip_03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>equip_04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>equip_05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>equip_06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>equip_07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>equip_08</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -655,6 +690,9 @@
       <c r="C2" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="E2" s="1" t="s">
         <v>34</v>
       </c>
@@ -675,6 +713,9 @@
       <c r="C3" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="E3" s="1" t="s">
         <v>35</v>
       </c>
@@ -695,6 +736,9 @@
       <c r="C4" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="E4" s="1" t="s">
         <v>37</v>
       </c>
@@ -715,6 +759,9 @@
       <c r="C5" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="E5" s="1" t="s">
         <v>36</v>
       </c>
@@ -735,6 +782,9 @@
       <c r="C6" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="E6" s="1" t="s">
         <v>34</v>
       </c>
@@ -755,6 +805,9 @@
       <c r="C7" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="D7" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="E7" s="1" t="s">
         <v>35</v>
       </c>
@@ -775,6 +828,9 @@
       <c r="C8" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="E8" s="1" t="s">
         <v>37</v>
       </c>
@@ -795,6 +851,9 @@
       <c r="C9" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="D9" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="E9" s="1" t="s">
         <v>36</v>
       </c>
@@ -815,6 +874,9 @@
       <c r="C10" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="D10" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="E10" s="1" t="s">
         <v>34</v>
       </c>
@@ -835,6 +897,9 @@
       <c r="C11" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="D11" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="E11" s="1" t="s">
         <v>35</v>
       </c>
@@ -855,6 +920,9 @@
       <c r="C12" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="D12" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="E12" s="1" t="s">
         <v>37</v>
       </c>
@@ -875,6 +943,9 @@
       <c r="C13" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="D13" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="E13" s="1" t="s">
         <v>36</v>
       </c>
@@ -895,6 +966,9 @@
       <c r="C14" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="D14" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="E14" s="1" t="s">
         <v>34</v>
       </c>
@@ -915,6 +989,9 @@
       <c r="C15" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="D15" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="E15" s="1" t="s">
         <v>35</v>
       </c>
@@ -935,6 +1012,9 @@
       <c r="C16" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="D16" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="E16" s="1" t="s">
         <v>37</v>
       </c>
@@ -955,6 +1035,9 @@
       <c r="C17" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="D17" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="E17" s="1" t="s">
         <v>36</v>
       </c>
@@ -975,6 +1058,9 @@
       <c r="C18" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="D18" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="E18" s="1" t="s">
         <v>34</v>
       </c>
@@ -995,6 +1081,9 @@
       <c r="C19" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="D19" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="E19" s="1" t="s">
         <v>35</v>
       </c>
@@ -1015,6 +1104,9 @@
       <c r="C20" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="D20" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="E20" s="1" t="s">
         <v>37</v>
       </c>
@@ -1035,6 +1127,9 @@
       <c r="C21" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="D21" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="E21" s="1" t="s">
         <v>36</v>
       </c>
@@ -1055,6 +1150,9 @@
       <c r="C22" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="D22" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="E22" s="1" t="s">
         <v>34</v>
       </c>
@@ -1075,6 +1173,9 @@
       <c r="C23" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="D23" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="E23" s="1" t="s">
         <v>35</v>
       </c>
@@ -1095,6 +1196,9 @@
       <c r="C24" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="D24" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="E24" s="1" t="s">
         <v>37</v>
       </c>
@@ -1115,6 +1219,9 @@
       <c r="C25" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="D25" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="E25" s="1" t="s">
         <v>36</v>
       </c>
@@ -1135,6 +1242,9 @@
       <c r="C26" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="D26" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="E26" s="1" t="s">
         <v>34</v>
       </c>
@@ -1155,6 +1265,9 @@
       <c r="C27" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="D27" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="E27" s="1" t="s">
         <v>35</v>
       </c>
@@ -1175,6 +1288,9 @@
       <c r="C28" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="D28" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="E28" s="1" t="s">
         <v>37</v>
       </c>
@@ -1195,6 +1311,9 @@
       <c r="C29" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="D29" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="E29" s="1" t="s">
         <v>36</v>
       </c>
@@ -1215,6 +1334,9 @@
       <c r="C30" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="D30" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="E30" s="1" t="s">
         <v>34</v>
       </c>
@@ -1235,6 +1357,9 @@
       <c r="C31" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="D31" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="E31" s="1" t="s">
         <v>35</v>
       </c>
@@ -1255,6 +1380,9 @@
       <c r="C32" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="D32" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="E32" s="1" t="s">
         <v>37</v>
       </c>
@@ -1274,6 +1402,9 @@
       </c>
       <c r="C33" s="1" t="s">
         <v>47</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>36</v>

--- a/config/excel/equipments.xlsx
+++ b/config/excel/equipments.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20371"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F30698E-3043-4497-87E1-0A22058B1F91}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F3F8031-7B79-486B-AD40-A174827174B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="72">
   <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -191,17 +191,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>生命+20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>生命+10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>生命+40</t>
-  </si>
-  <si>
     <t>鞋</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -314,6 +303,10 @@
   </si>
   <si>
     <t>equip_08</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命+0.5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -682,7 +675,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
@@ -691,7 +684,7 @@
         <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>34</v>
@@ -705,7 +698,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B3" s="1">
         <v>0</v>
@@ -714,7 +707,7 @@
         <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>35</v>
@@ -728,7 +721,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B4" s="1">
         <v>0</v>
@@ -737,7 +730,7 @@
         <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>37</v>
@@ -751,7 +744,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B5" s="1">
         <v>0</v>
@@ -760,7 +753,7 @@
         <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>36</v>
@@ -774,7 +767,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B6" s="1">
         <v>0</v>
@@ -783,21 +776,21 @@
         <v>41</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B7" s="1">
         <v>0</v>
@@ -806,21 +799,21 @@
         <v>41</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B8" s="1">
         <v>0</v>
@@ -829,21 +822,21 @@
         <v>41</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B9" s="1">
         <v>0</v>
@@ -852,205 +845,205 @@
         <v>41</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B10" s="1">
         <v>0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B11" s="1">
         <v>0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B12" s="1">
         <v>0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B13" s="1">
         <v>0</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B14" s="1">
         <v>0</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B15" s="1">
         <v>0</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B16" s="1">
         <v>0</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B17" s="1">
         <v>0</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B18" s="1">
         <v>0</v>
@@ -1059,7 +1052,7 @@
         <v>33</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>34</v>
@@ -1073,7 +1066,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B19" s="1">
         <v>0</v>
@@ -1082,21 +1075,21 @@
         <v>33</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B20" s="1">
         <v>0</v>
@@ -1105,21 +1098,21 @@
         <v>33</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B21" s="1">
         <v>0</v>
@@ -1128,7 +1121,7 @@
         <v>33</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>36</v>
@@ -1142,85 +1135,85 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B22" s="1">
         <v>0</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B23" s="1">
         <v>0</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B24" s="1">
         <v>0</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B25" s="1">
         <v>0</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>36</v>
@@ -1234,7 +1227,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B26" s="1">
         <v>0</v>
@@ -1243,21 +1236,21 @@
         <v>41</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B27" s="1">
         <v>0</v>
@@ -1266,21 +1259,21 @@
         <v>41</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B28" s="1">
         <v>0</v>
@@ -1289,21 +1282,21 @@
         <v>41</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B29" s="1">
         <v>0</v>
@@ -1312,7 +1305,7 @@
         <v>41</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>36</v>
@@ -1326,85 +1319,85 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B30" s="1">
         <v>0</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B31" s="1">
         <v>0</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B32" s="1">
         <v>0</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B33" s="1">
         <v>0</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>36</v>
@@ -1434,7 +1427,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">

--- a/config/excel/equipments.xlsx
+++ b/config/excel/equipments.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20371"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F3F8031-7B79-486B-AD40-A174827174B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F009D4-69F9-47D7-8680-FB41549F7403}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="79">
   <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -59,10 +59,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ui展示描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>每个子弹1%概率秒杀血量低于30%的小怪</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -195,26 +191,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>暴击率+5%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>头盔</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>气力上限+5%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>暴风大剑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>暴击伤害+10%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>攻击力+20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -223,26 +207,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>暴击率基础值+5%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>气力上限基础值+5%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击伤害倍率基础值+10%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>移速基础值+10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>气力回复速度基础值+5%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>丛林甲</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -307,6 +271,70 @@
   </si>
   <si>
     <t>生命+0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击力+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受击无敌时间+0.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级每级实际效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受击无敌时间+0.01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击率+0.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>气力上限+10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动速度+10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>气力回复速度+3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>划线气力消耗-0.01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击率+0.01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>气力上限+2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击力+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动速度+2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>气力回复速度+0.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>划线气力消耗-0.002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击伤害倍率基础值+0.3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -644,10 +672,9 @@
     <col min="4" max="4" width="8.88671875" style="1" customWidth="1"/>
     <col min="5" max="5" width="8.88671875" style="1"/>
     <col min="6" max="6" width="31.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.21875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" customWidth="1"/>
-    <col min="10" max="10" width="22.33203125" customWidth="1"/>
-    <col min="11" max="11" width="21.6640625" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" customWidth="1"/>
+    <col min="8" max="8" width="22.33203125" customWidth="1"/>
+    <col min="9" max="9" width="21.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -655,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
@@ -670,743 +697,743 @@
         <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B3" s="1">
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B4" s="1">
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B5" s="1">
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B6" s="1">
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B7" s="1">
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B8" s="1">
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B9" s="1">
         <v>0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B10" s="1">
         <v>0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B11" s="1">
         <v>0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B12" s="1">
         <v>0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B13" s="1">
         <v>0</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B14" s="1">
         <v>0</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B15" s="1">
         <v>0</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B16" s="1">
         <v>0</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B17" s="1">
         <v>0</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B18" s="1">
         <v>0</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="F18" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B19" s="1">
         <v>0</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B20" s="1">
         <v>0</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B21" s="1">
         <v>0</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B22" s="1">
         <v>0</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B23" s="1">
         <v>0</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B24" s="1">
         <v>0</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B25" s="1">
         <v>0</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B26" s="1">
         <v>0</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B27" s="1">
         <v>0</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B28" s="1">
         <v>0</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B29" s="1">
         <v>0</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B30" s="1">
         <v>0</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>71</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B31" s="1">
         <v>0</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B32" s="1">
         <v>0</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B33" s="1">
         <v>0</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1427,15 +1454,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1443,23 +1470,23 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1467,7 +1494,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1475,7 +1502,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1483,63 +1510,63 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/config/excel/equipments.xlsx
+++ b/config/excel/equipments.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20371"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F009D4-69F9-47D7-8680-FB41549F7403}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D769554-ED7C-4539-ACDB-CF75E40D4E18}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,6 +11,9 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="草稿，无视此sheet" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'草稿，无视此sheet'!$G$1:$G$123</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -21,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="152">
   <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -175,10 +178,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻击力+10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>是否为稀有装备</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -199,10 +198,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻击力+20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>轻灵之靴</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -274,67 +269,292 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻击力+1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>受击无敌时间+0.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>升级每级实际效果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>受击无敌时间+0.01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击率+0.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>气力上限+10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>移动速度+10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>气力回复速度+3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>划线气力消耗-0.01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击率+0.01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>气力上限+2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击力+1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>移动速度+2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>气力回复速度+0.8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>划线气力消耗-0.002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击伤害倍率基础值+0.3</t>
+    <t>受击无敌时间+5%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受击无敌时间+1%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击率+3%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>气力上限+3%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击率+0.5%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>气力上限+0.5%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击伤害倍率+5%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动速度+3%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>气力回复速度+5%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>划线气力消耗-5%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "base_attack",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "value": 52,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "基础攻击力"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  },</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "base_hp",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "value": 3.0,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "基础生命（心数制：3 颗心）"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "base_ki",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "value": 234,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "基础气力上限"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "base_crit_rate",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "value": 0.08,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "暴击率"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "base_crit_damage",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "value": 1.6,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "暴击伤害倍率"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "attack_speed",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "value": 2850,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "路径冲刺速度 px/s"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "move_speed",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "value": 60,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "摇杆移动速度 px/s"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "hitbox_radius",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "value": 22,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "碰撞半径"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "trigger_radius_ratio",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "value": 0.06,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "触发圈相对屏宽比例"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "trigger_radius_min",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "value": 55,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "触发圈最小半径"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "trigger_ring_fade_in",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "value": 0.35,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "攻击后触发圈渐显时长(s)"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "ki_per_pixel",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "value": 0.18,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "划线每像素消耗气力"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "basic_attack_speed",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "value": 2,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "普攻攻速(次/秒，决定普攻子弹频率)"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "ki_regen_speed",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "气力回复速度(点/秒)"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "combo_damage_bonus",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "value": 0.01,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "每连击伤害加成"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "invincible_time",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "value": 0.45,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "受击无敌时间"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "auto_bullet_damage_mult",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "value": 0.5,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "普攻子弹伤害倍率"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "auto_bullet_speed",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "value": 420,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "普攻子弹速度"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "auto_bullet_life",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "value": 0.9,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "普攻子弹存活时间（已弃用：当前由 auto_bullet_range 控制飞行距离，保留仅供绘制兜底）"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "auto_bullet_range",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "value": 378,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "普攻子弹有效射程(px)：怪进入此距离才开火，子弹飞行此距离后消失"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "character_folder",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "value": "Swordsman",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "主角素材文件夹"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "sprite_prefix",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "主角精灵前缀"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "sprite_scale",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "value": 3.7,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "显示缩放(100px素材，2=200px显示)"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "key": "auto_bullet_pierce_range_mul",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "value": 0.85,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "description": "穿透子弹攻击距离倍率(相对 auto_bullet_range)"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  }</t>
+  </si>
+  <si>
+    <t>]</t>
+  </si>
+  <si>
+    <t>攻击力+3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击力+0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动速度+0.3%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>气力回复速度+0.5%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>划线气力消耗-0.5%</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -682,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
@@ -697,12 +917,12 @@
         <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
@@ -711,21 +931,21 @@
         <v>32</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>37</v>
+        <v>147</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>63</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B3" s="1">
         <v>0</v>
@@ -734,21 +954,21 @@
         <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>63</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B4" s="1">
         <v>0</v>
@@ -757,21 +977,21 @@
         <v>32</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>63</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B5" s="1">
         <v>0</v>
@@ -780,297 +1000,297 @@
         <v>32</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>63</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B6" s="1">
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B7" s="1">
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B8" s="1">
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B9" s="1">
         <v>0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B10" s="1">
         <v>0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B11" s="1">
         <v>0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B12" s="1">
         <v>0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B13" s="1">
         <v>0</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B14" s="1">
         <v>0</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B15" s="1">
         <v>0</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B16" s="1">
         <v>0</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B17" s="1">
         <v>0</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B18" s="1">
         <v>0</v>
@@ -1079,21 +1299,21 @@
         <v>32</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" s="1">
         <v>0</v>
@@ -1102,21 +1322,21 @@
         <v>32</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="1">
         <v>0</v>
@@ -1125,21 +1345,21 @@
         <v>32</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21" s="1">
         <v>0</v>
@@ -1148,7 +1368,7 @@
         <v>32</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>35</v>
@@ -1157,21 +1377,21 @@
         <v>3</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B22" s="1">
         <v>0</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>33</v>
@@ -1180,21 +1400,21 @@
         <v>69</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>75</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B23" s="1">
         <v>0</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>34</v>
@@ -1203,21 +1423,21 @@
         <v>69</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>75</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B24" s="1">
         <v>0</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>36</v>
@@ -1226,21 +1446,21 @@
         <v>69</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>75</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B25" s="1">
         <v>0</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>35</v>
@@ -1249,21 +1469,21 @@
         <v>18</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>75</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B26" s="1">
         <v>0</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>33</v>
@@ -1272,21 +1492,21 @@
         <v>70</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>76</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B27" s="1">
         <v>0</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>34</v>
@@ -1295,21 +1515,21 @@
         <v>70</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>76</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B28" s="1">
         <v>0</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>36</v>
@@ -1318,21 +1538,21 @@
         <v>70</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>76</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B29" s="1">
         <v>0</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>35</v>
@@ -1341,21 +1561,21 @@
         <v>17</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>76</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B30" s="1">
         <v>0</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>33</v>
@@ -1364,67 +1584,67 @@
         <v>71</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>77</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B31" s="1">
         <v>0</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>77</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B32" s="1">
         <v>0</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>77</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B33" s="1">
         <v>0</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>35</v>
@@ -1433,7 +1653,7 @@
         <v>29</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>77</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -1445,131 +1665,790 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A76402FA-0AFF-44EB-800A-CCBF43C501FE}">
-  <dimension ref="A1:B15"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.33203125" customWidth="1"/>
     <col min="2" max="2" width="26.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="G15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G23" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G24" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G25" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G26" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G27" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G29" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G30" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G31" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G32" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G33" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G34" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G35" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G36" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G37" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G38" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G39" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="40" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G40" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="41" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G41" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="42" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G42" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G43" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G44" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="45" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G45" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G46" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="47" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G47" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G48" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="49" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G49" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="50" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G50" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="51" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G51" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="52" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G52" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="53" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G53" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="54" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G54" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="55" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G55" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="56" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G56" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G57" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G58" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="59" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G59" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="60" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G60" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="61" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G61" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="62" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G62" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="63" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G63" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="64" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G64" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="65" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G65" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="66" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G66" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="67" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G67" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="68" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G68" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="69" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G69" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="70" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G70" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="71" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G71" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="72" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G72" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="73" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G73" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G74" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="75" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G75" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="76" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G76" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="77" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G77" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G78" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="79" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G79" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="80" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G80" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="81" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G81" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="82" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G82" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="83" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G83" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="84" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G84" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="85" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G85" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="86" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G86" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="87" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G87" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="88" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G88" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="89" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G89" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="90" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G90" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="91" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G91" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="92" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G92" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="93" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G93" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="94" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G94" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="95" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G95" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="96" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G96" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="97" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G97" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="98" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G98" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="99" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G99" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="100" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G100" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="101" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G101" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="102" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G102" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="103" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G103" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="104" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G104" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="105" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G105" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="106" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G106" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="107" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G107" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="108" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G108" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="109" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G109" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="110" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G110" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="111" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G111" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="112" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G112" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="113" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G113" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="114" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G114" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="115" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G115" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="116" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G116" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="117" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G117" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="118" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G118" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="119" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G119" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="120" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G120" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="121" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G121" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="122" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G122" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="123" spans="7:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G123" t="s">
+        <v>146</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="G1:G123" xr:uid="{AEAC97A3-1071-42A5-9C93-3C29861687DB}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="&quot;description&quot;: &quot;暴击率&quot;"/>
+        <filter val="&quot;description&quot;: &quot;暴击伤害倍率&quot;"/>
+        <filter val="&quot;description&quot;: &quot;触发圈相对屏宽比例&quot;"/>
+        <filter val="&quot;description&quot;: &quot;触发圈最小半径&quot;"/>
+        <filter val="&quot;description&quot;: &quot;穿透子弹攻击距离倍率(相对 auto_bullet_range)&quot;"/>
+        <filter val="&quot;description&quot;: &quot;攻击后触发圈渐显时长(s)&quot;"/>
+        <filter val="&quot;description&quot;: &quot;划线每像素消耗气力&quot;"/>
+        <filter val="&quot;description&quot;: &quot;基础攻击力&quot;"/>
+        <filter val="&quot;description&quot;: &quot;基础气力上限&quot;"/>
+        <filter val="&quot;description&quot;: &quot;基础生命（心数制：3 颗心）&quot;"/>
+        <filter val="&quot;description&quot;: &quot;路径冲刺速度 px/s&quot;"/>
+        <filter val="&quot;description&quot;: &quot;每连击伤害加成&quot;"/>
+        <filter val="&quot;description&quot;: &quot;碰撞半径&quot;"/>
+        <filter val="&quot;description&quot;: &quot;普攻攻速(次/秒，决定普攻子弹频率)&quot;"/>
+        <filter val="&quot;description&quot;: &quot;普攻子弹存活时间（已弃用：当前由 auto_bullet_range 控制飞行距离，保留仅供绘制兜底）&quot;"/>
+        <filter val="&quot;description&quot;: &quot;普攻子弹伤害倍率&quot;"/>
+        <filter val="&quot;description&quot;: &quot;普攻子弹速度&quot;"/>
+        <filter val="&quot;description&quot;: &quot;普攻子弹有效射程(px)：怪进入此距离才开火，子弹飞行此距离后消失&quot;"/>
+        <filter val="&quot;description&quot;: &quot;气力回复速度(点/秒)&quot;"/>
+        <filter val="&quot;description&quot;: &quot;受击无敌时间&quot;"/>
+        <filter val="&quot;description&quot;: &quot;显示缩放(100px素材，2=200px显示)&quot;"/>
+        <filter val="&quot;description&quot;: &quot;摇杆移动速度 px/s&quot;"/>
+        <filter val="&quot;description&quot;: &quot;主角精灵前缀&quot;"/>
+        <filter val="&quot;description&quot;: &quot;主角素材文件夹&quot;"/>
+        <filter val="&quot;key&quot;: &quot;attack_speed&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;auto_bullet_damage_mult&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;auto_bullet_life&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;auto_bullet_pierce_range_mul&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;auto_bullet_range&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;auto_bullet_speed&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;base_attack&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;base_crit_damage&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;base_crit_rate&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;base_hp&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;base_ki&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;basic_attack_speed&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;character_folder&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;combo_damage_bonus&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;hitbox_radius&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;invincible_time&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;ki_per_pixel&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;ki_regen_speed&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;move_speed&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;sprite_prefix&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;sprite_scale&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;trigger_radius_min&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;trigger_radius_ratio&quot;,"/>
+        <filter val="&quot;key&quot;: &quot;trigger_ring_fade_in&quot;,"/>
+        <filter val="&quot;value&quot;: &quot;Swordsman&quot;,"/>
+        <filter val="&quot;value&quot;: 0.01,"/>
+        <filter val="&quot;value&quot;: 0.06,"/>
+        <filter val="&quot;value&quot;: 0.08,"/>
+        <filter val="&quot;value&quot;: 0.18,"/>
+        <filter val="&quot;value&quot;: 0.35,"/>
+        <filter val="&quot;value&quot;: 0.45,"/>
+        <filter val="&quot;value&quot;: 0.5,"/>
+        <filter val="&quot;value&quot;: 0.85,"/>
+        <filter val="&quot;value&quot;: 0.9,"/>
+        <filter val="&quot;value&quot;: 1.6,"/>
+        <filter val="&quot;value&quot;: 2,"/>
+        <filter val="&quot;value&quot;: 22,"/>
+        <filter val="&quot;value&quot;: 234,"/>
+        <filter val="&quot;value&quot;: 2850,"/>
+        <filter val="&quot;value&quot;: 3.0,"/>
+        <filter val="&quot;value&quot;: 3.7,"/>
+        <filter val="&quot;value&quot;: 378,"/>
+        <filter val="&quot;value&quot;: 420,"/>
+        <filter val="&quot;value&quot;: 52,"/>
+        <filter val="&quot;value&quot;: 55,"/>
+        <filter val="&quot;value&quot;: 60,"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
